--- a/02_DIA_inicio_2026_analisis_assets/rbd_9625_escuela-basica-villa-la-cultura_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9625_escuela-basica-villa-la-cultura_nt1_rubricas.xlsx
@@ -1704,13 +1704,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F7BB653-B744-4D9B-81BF-181E9E7DC054}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28A5B56F-1683-4C6E-AA72-B20B4B67F6F4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC3CB46B-2E45-4514-82AF-4D30043AE511}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA0C0594-3E38-4038-B74F-DE88E24F9446}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFA4208-B513-428D-B5EF-83AE4AB3157C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3D38FD5-2D97-4B04-8885-384BBA05304F}"/>
 </file>